--- a/00-TrainRnns/tau-3/Y_otm/Metricas.xlsx
+++ b/00-TrainRnns/tau-3/Y_otm/Metricas.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E51"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,14 +470,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.9998117927938655</v>
+        <v>0.9986545955373483</v>
       </c>
       <c r="E2" t="n">
-        <v>1.480417391672839e-05</v>
+        <v>0.0001058280501714674</v>
       </c>
     </row>
     <row r="3">
@@ -493,14 +493,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.9952066793360069</v>
+        <v>0.9992522452713695</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003770373845179628</v>
+        <v>5.881757280743408e-05</v>
       </c>
     </row>
     <row r="4">
@@ -516,14 +516,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.9990937930649372</v>
+        <v>0.9943255528123531</v>
       </c>
       <c r="E4" t="n">
-        <v>7.128125084447774e-05</v>
+        <v>0.000446345837508273</v>
       </c>
     </row>
     <row r="5">
@@ -539,14 +539,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.9995844663618629</v>
+        <v>0.9997339220831416</v>
       </c>
       <c r="E5" t="n">
-        <v>3.268542354767793e-05</v>
+        <v>2.092939923754009e-05</v>
       </c>
     </row>
     <row r="6">
@@ -562,20 +562,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.9990337036595632</v>
+        <v>0.9902086044674883</v>
       </c>
       <c r="E6" t="n">
-        <v>7.600781804654852e-05</v>
+        <v>0.0007701805118299186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ZZx2</t>
+          <t>ZZx1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -585,14 +585,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.9931314902373967</v>
+        <v>0.9975298708472693</v>
       </c>
       <c r="E7" t="n">
-        <v>0.004061232115372802</v>
+        <v>0.0001942976697059355</v>
       </c>
     </row>
     <row r="8">
@@ -608,14 +608,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.9857774875552193</v>
+        <v>0.9945103620470628</v>
       </c>
       <c r="E8" t="n">
-        <v>0.008409527874084237</v>
+        <v>0.003245928844365197</v>
       </c>
     </row>
     <row r="9">
@@ -631,14 +631,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.9823805775604157</v>
+        <v>0.9876614333285169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.01041806254037231</v>
+        <v>0.007295583023951689</v>
       </c>
     </row>
     <row r="10">
@@ -654,14 +654,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9786393656297544</v>
+        <v>0.9863250866823713</v>
       </c>
       <c r="E10" t="n">
-        <v>0.01263017704095047</v>
+        <v>0.008085741894533292</v>
       </c>
     </row>
     <row r="11">
@@ -677,20 +677,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.987749552432535</v>
+        <v>0.982150314957204</v>
       </c>
       <c r="E11" t="n">
-        <v>0.007243479707863419</v>
+        <v>0.0105542128715875</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ZZxReto</t>
+          <t>ZZx2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -700,20 +700,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.753924524622451</v>
+        <v>0.9804747537246968</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02016413890796424</v>
+        <v>0.0115449435138851</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ZZxReto</t>
+          <t>ZZx2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -723,14 +723,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.8158300136796462</v>
+        <v>0.9914719659239283</v>
       </c>
       <c r="E13" t="n">
-        <v>0.01509142339822258</v>
+        <v>0.005042480402271255</v>
       </c>
     </row>
     <row r="14">
@@ -746,14 +746,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.6365510102029051</v>
+        <v>0.8156148870671459</v>
       </c>
       <c r="E14" t="n">
-        <v>0.0297820654617601</v>
+        <v>0.01510905149744946</v>
       </c>
     </row>
     <row r="15">
@@ -769,14 +769,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.6312490303788336</v>
+        <v>0.8012379875171317</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03021652508231257</v>
+        <v>0.01628713638846735</v>
       </c>
     </row>
     <row r="16">
@@ -792,20 +792,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.7188945893960833</v>
+        <v>0.8180802879202024</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0230345935063257</v>
+        <v>0.01490702939350525</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ZZy1</t>
+          <t>ZZxReto</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -815,20 +815,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-8.120456015028749</v>
+        <v>0.794741027950464</v>
       </c>
       <c r="E17" t="n">
-        <v>1.160768489802872</v>
+        <v>0.01681951611863231</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ZZy1</t>
+          <t>ZZxReto</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -838,20 +838,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-7.148214149666172</v>
+        <v>0.8032319521603384</v>
       </c>
       <c r="E18" t="n">
-        <v>1.03703040917177</v>
+        <v>0.01612374513632611</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ZZy1</t>
+          <t>ZZxReto</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -861,14 +861,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-8.110301884635179</v>
+        <v>0.8073511280846135</v>
       </c>
       <c r="E19" t="n">
-        <v>1.159476164662244</v>
+        <v>0.01578620790147574</v>
       </c>
     </row>
     <row r="20">
@@ -884,14 +884,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-10.0039896202919</v>
+        <v>-6.740881903381998</v>
       </c>
       <c r="E20" t="n">
-        <v>1.400487474782525</v>
+        <v>0.9851888745392712</v>
       </c>
     </row>
     <row r="21">
@@ -907,20 +907,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-8.308602571009176</v>
+        <v>-7.362374233857409</v>
       </c>
       <c r="E21" t="n">
-        <v>1.184714068103687</v>
+        <v>1.06428675217623</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ZZy2</t>
+          <t>ZZy1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -930,20 +930,20 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-40.26575896687407</v>
+        <v>-7.186987921544885</v>
       </c>
       <c r="E22" t="n">
-        <v>2.588197392634018</v>
+        <v>1.041965181353495</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ZZy2</t>
+          <t>ZZy1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -953,20 +953,20 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-36.606161494118</v>
+        <v>-9.478825228144185</v>
       </c>
       <c r="E23" t="n">
-        <v>2.35866664185634</v>
+        <v>1.333649338907844</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ZZy2</t>
+          <t>ZZy1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -976,20 +976,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-37.07347320820794</v>
+        <v>-7.660226538066448</v>
       </c>
       <c r="E24" t="n">
-        <v>2.387976534373423</v>
+        <v>1.10219467791715</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ZZy2</t>
+          <t>ZZy1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -999,14 +999,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-38.63071027922806</v>
+        <v>-7.651635751588616</v>
       </c>
       <c r="E25" t="n">
-        <v>2.485646782730244</v>
+        <v>1.10110132093701</v>
       </c>
     </row>
     <row r="26">
@@ -1022,20 +1022,20 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-38.12471100308149</v>
+        <v>-37.30894090844242</v>
       </c>
       <c r="E26" t="n">
-        <v>2.453910397892429</v>
+        <v>2.402745119831542</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>LSG-1</t>
+          <t>ZZy2</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1045,20 +1045,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-0.004856769834098218</v>
+        <v>-37.65689712954374</v>
       </c>
       <c r="E27" t="n">
-        <v>0.3671901410248296</v>
+        <v>2.424569009825378</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LSG-1</t>
+          <t>ZZy2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-0.06301272596940444</v>
+        <v>-36.53172755602736</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3884412231450033</v>
+        <v>2.353998129042985</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LSG-1</t>
+          <t>ZZy2</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1091,20 +1091,20 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>0.2524674866047645</v>
+        <v>-37.06220206309609</v>
       </c>
       <c r="E29" t="n">
-        <v>0.2731598942798182</v>
+        <v>2.387269605696456</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LSG-1</t>
+          <t>ZZy2</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1114,20 +1114,20 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>0.2287099997135913</v>
+        <v>-40.97016132406507</v>
       </c>
       <c r="E30" t="n">
-        <v>0.2818412459150424</v>
+        <v>2.632377661939389</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LSG-1</t>
+          <t>ZZy2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1141,16 +1141,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0.1149399202055461</v>
+        <v>-37.88734474790549</v>
       </c>
       <c r="E31" t="n">
-        <v>0.3234145853133154</v>
+        <v>2.439022734654755</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LSG-2</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1160,20 +1160,20 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-0.4710068297644598</v>
+        <v>-0.01170031422651197</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1235986981044904</v>
+        <v>0.3696908775536535</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LSG-2</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1183,20 +1183,20 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2313647814686659</v>
+        <v>0.2769473459701337</v>
       </c>
       <c r="E33" t="n">
-        <v>0.0645831891500771</v>
+        <v>0.2642145766161655</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>LSG-2</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1206,20 +1206,20 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-0.549426994932535</v>
+        <v>-0.06704156096396141</v>
       </c>
       <c r="E34" t="n">
-        <v>0.130187811168952</v>
+        <v>0.3899134215062299</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LSG-2</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1229,20 +1229,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-0.294456661511119</v>
+        <v>0.1089802503825436</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1087643883618662</v>
+        <v>0.3255923404605799</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>LSG-2</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1252,20 +1252,20 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>-0.2450840169653079</v>
+        <v>0.1396826672743564</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1046159408738181</v>
+        <v>0.314373204433692</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ZZx1-inv</t>
+          <t>LSG-1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1275,20 +1275,20 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-1.390420356278398</v>
+        <v>0.09781553762358264</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1602264086804516</v>
+        <v>0.3296720984674263</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ZZx1-inv</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1298,20 +1298,20 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-1.867446675016547</v>
+        <v>-0.05391917302884641</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1922007907997814</v>
+        <v>0.08855365934268608</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ZZx1-inv</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1321,20 +1321,20 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-1.288435481975966</v>
+        <v>-0.1377720976115562</v>
       </c>
       <c r="E39" t="n">
-        <v>0.153390510506188</v>
+        <v>0.09559925022708494</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ZZx1-inv</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1344,20 +1344,20 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>-1.403545387810471</v>
+        <v>0.2400307210157625</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1611061605034639</v>
+        <v>0.06385504919572701</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ZZx1-inv</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1367,20 +1367,20 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>-1.477558541463074</v>
+        <v>-0.9391292073975821</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1660671548213561</v>
+        <v>0.162931837324719</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>zzx2-inv2</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1390,20 +1390,20 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0.05132319758644166</v>
+        <v>-0.02274421324467002</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5775555927149743</v>
+        <v>0.08593423952435592</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>zzx2-inv2</t>
+          <t>LSG-2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1413,20 +1413,20 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-0.1655294406607464</v>
+        <v>-0.1443991587838209</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7095757429874614</v>
+        <v>0.09615607710006546</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>zzx2-inv2</t>
+          <t>ZZx1-inv</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1436,20 +1436,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>-0.09727208631573236</v>
+        <v>-1.876868380045798</v>
       </c>
       <c r="E44" t="n">
-        <v>0.6680205825307128</v>
+        <v>0.1928323140197533</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>zzx2-inv2</t>
+          <t>ZZx1-inv</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1459,20 +1459,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.0835196676237403</v>
+        <v>-1.723012368173601</v>
       </c>
       <c r="E45" t="n">
-        <v>0.5579543425437745</v>
+        <v>0.18251956874404</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>zzx2-inv2</t>
+          <t>ZZx1-inv</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1482,20 +1482,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENSEMBLE</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>-0.02434084472023779</v>
+        <v>-1.857128860536619</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6236199538234847</v>
+        <v>0.1915092026633233</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>semiCirc</t>
+          <t>ZZx1-inv</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1505,20 +1505,20 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-1.72568044496412</v>
+        <v>-1.700548660137354</v>
       </c>
       <c r="E47" t="n">
-        <v>0.4143006059229598</v>
+        <v>0.1810138589826415</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>semiCirc</t>
+          <t>ZZx1-inv</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1528,20 +1528,20 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>-1.815746875847191</v>
+        <v>-1.628901331125628</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4279906101775363</v>
+        <v>0.1762114424583076</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>semiCirc</t>
+          <t>ZZx1-inv</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1551,20 +1551,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>ENSEMBLE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-0.8748157278102038</v>
+        <v>-1.753857911716516</v>
       </c>
       <c r="E49" t="n">
-        <v>0.2849700497579374</v>
+        <v>0.1845871007798583</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>semiCirc</t>
+          <t>zzx2-inv2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1574,37 +1574,267 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-0.154717819657006</v>
+        <v>-0.1620830845842458</v>
       </c>
       <c r="E50" t="n">
-        <v>0.1755159131870406</v>
+        <v>0.7074775972107268</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.2408705163932491</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.4621589541732883</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.1690468865763954</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7117171683448508</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.008062016161738739</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.603893052654679</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1740381150131688</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.5028466015295168</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>zzx2-inv2</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ENSEMBLE</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.03892006800563463</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.5851066331096996</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
           <t>semiCirc</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>y</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>-1.497617635649558</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.3796352950050618</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>-0.1913034945631833</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.1810768978981185</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>-1.826582000880982</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.4296375379658045</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>-0.215911716214749</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.1848173221139383</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>-0.8642610609724162</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2833657513251224</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>semiCirc</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
         <is>
           <t>ENSEMBLE</t>
         </is>
       </c>
-      <c r="D51" t="n">
-        <v>-1.054114152363842</v>
-      </c>
-      <c r="E51" t="n">
-        <v>0.3122232246746258</v>
+      <c r="D61" t="n">
+        <v>-0.8258840894912616</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.2775324913890554</v>
       </c>
     </row>
   </sheetData>
@@ -1618,7 +1848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1639,22 +1869,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
     </row>
@@ -1670,19 +1905,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1149399202055461</v>
+        <v>0.09781553762358264</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.004856769834098218</v>
+        <v>-0.06704156096396141</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2287099997135913</v>
+        <v>0.1089802503825436</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2524674866047645</v>
+        <v>-0.01170031422651197</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.06301272596940444</v>
+        <v>0.2769473459701337</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.1396826672743564</v>
       </c>
     </row>
     <row r="3">
@@ -1697,19 +1935,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.2450840169653079</v>
+        <v>-0.1443991587838209</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.4710068297644598</v>
+        <v>0.2400307210157625</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.294456661511119</v>
+        <v>-0.9391292073975821</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.549426994932535</v>
+        <v>-0.05391917302884641</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2313647814686659</v>
+        <v>-0.1377720976115562</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-0.02274421324467002</v>
       </c>
     </row>
     <row r="4">
@@ -1724,19 +1965,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.9990337036595632</v>
+        <v>0.9975298708472693</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9998117927938655</v>
+        <v>0.9943255528123531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9995844663618629</v>
+        <v>0.9997339220831416</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9990937930649372</v>
+        <v>0.9986545955373483</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9952066793360069</v>
+        <v>0.9992522452713695</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.9902086044674883</v>
       </c>
     </row>
     <row r="5">
@@ -1751,19 +1995,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1.477558541463074</v>
+        <v>-1.753857911716516</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.390420356278398</v>
+        <v>-1.857128860536619</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.403545387810471</v>
+        <v>-1.700548660137354</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.288435481975966</v>
+        <v>-1.876868380045798</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.867446675016547</v>
+        <v>-1.723012368173601</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-1.628901331125628</v>
       </c>
     </row>
     <row r="6">
@@ -1778,19 +2025,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.987749552432535</v>
+        <v>0.9914719659239283</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9931314902373967</v>
+        <v>0.9863250866823713</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9786393656297544</v>
+        <v>0.982150314957204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9823805775604157</v>
+        <v>0.9945103620470628</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9857774875552193</v>
+        <v>0.9876614333285169</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.9804747537246968</v>
       </c>
     </row>
     <row r="7">
@@ -1805,19 +2055,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.7188945893960833</v>
+        <v>0.8073511280846135</v>
       </c>
       <c r="D7" t="n">
-        <v>0.753924524622451</v>
+        <v>0.8180802879202024</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6312490303788336</v>
+        <v>0.794741027950464</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6365510102029051</v>
+        <v>0.8156148870671459</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8158300136796462</v>
+        <v>0.8012379875171317</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.8032319521603384</v>
       </c>
     </row>
     <row r="8">
@@ -1832,19 +2085,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-8.308602571009176</v>
+        <v>-7.651635751588616</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.120456015028749</v>
+        <v>-7.186987921544885</v>
       </c>
       <c r="E8" t="n">
-        <v>-10.0039896202919</v>
+        <v>-9.478825228144185</v>
       </c>
       <c r="F8" t="n">
-        <v>-8.110301884635179</v>
+        <v>-6.740881903381998</v>
       </c>
       <c r="G8" t="n">
-        <v>-7.148214149666172</v>
+        <v>-7.362374233857409</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-7.660226538066448</v>
       </c>
     </row>
     <row r="9">
@@ -1859,19 +2115,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-38.12471100308149</v>
+        <v>-37.88734474790549</v>
       </c>
       <c r="D9" t="n">
-        <v>-40.26575896687407</v>
+        <v>-36.53172755602736</v>
       </c>
       <c r="E9" t="n">
-        <v>-38.63071027922806</v>
+        <v>-37.06220206309609</v>
       </c>
       <c r="F9" t="n">
-        <v>-37.07347320820794</v>
+        <v>-37.30894090844242</v>
       </c>
       <c r="G9" t="n">
-        <v>-36.606161494118</v>
+        <v>-37.65689712954374</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-40.97016132406507</v>
       </c>
     </row>
     <row r="10">
@@ -1886,19 +2145,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1.054114152363842</v>
+        <v>-0.8258840894912616</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.72568044496412</v>
+        <v>-1.826582000880982</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.154717819657006</v>
+        <v>-0.215911716214749</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8748157278102038</v>
+        <v>-1.497617635649558</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.815746875847191</v>
+        <v>-0.1913034945631833</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.8642610609724162</v>
       </c>
     </row>
     <row r="11">
@@ -1913,19 +2175,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.02434084472023779</v>
+        <v>0.03892006800563463</v>
       </c>
       <c r="D11" t="n">
-        <v>0.05132319758644166</v>
+        <v>-0.1690468865763954</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0835196676237403</v>
+        <v>0.008062016161738739</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.09727208631573236</v>
+        <v>-0.1620830845842458</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.1655294406607464</v>
+        <v>0.2408705163932491</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.1740381150131688</v>
       </c>
     </row>
   </sheetData>
@@ -1939,7 +2204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1960,22 +2225,27 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>model_arch55_r0.9_Ld0.7_Lp0.3_seed1926</t>
+          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>model_arch61_r0.9_Ld0.5_Lp0.5_seed896</t>
+          <t>model_arch88_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>model_arch67_r0.01_Ld0.5_Lp0.5_seed679</t>
+          <t>model_arch89_r0.01_Ld0.5_Lp0.5_seed7093</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>model_arch76_r0.01_Ld0.5_Lp0.5_seed4080</t>
+          <t>model_arch94_r0.9_Ld0.7_Lp0.3_seed7093</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>model_arch95_r0.9_Ld0.7_Lp0.3_seed2243</t>
         </is>
       </c>
     </row>
@@ -1991,19 +2261,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3234145853133154</v>
+        <v>0.3296720984674263</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3671901410248296</v>
+        <v>0.3899134215062299</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2818412459150424</v>
+        <v>0.3255923404605799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2731598942798182</v>
+        <v>0.3696908775536535</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3884412231450033</v>
+        <v>0.2642145766161655</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.314373204433692</v>
       </c>
     </row>
     <row r="3">
@@ -2018,19 +2291,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1046159408738181</v>
+        <v>0.09615607710006546</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1235986981044904</v>
+        <v>0.06385504919572701</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1087643883618662</v>
+        <v>0.162931837324719</v>
       </c>
       <c r="F3" t="n">
-        <v>0.130187811168952</v>
+        <v>0.08855365934268608</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0645831891500771</v>
+        <v>0.09559925022708494</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.08593423952435592</v>
       </c>
     </row>
     <row r="4">
@@ -2045,19 +2321,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>7.600781804654852e-05</v>
+        <v>0.0001942976697059355</v>
       </c>
       <c r="D4" t="n">
-        <v>1.480417391672839e-05</v>
+        <v>0.000446345837508273</v>
       </c>
       <c r="E4" t="n">
-        <v>3.268542354767793e-05</v>
+        <v>2.092939923754009e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>7.128125084447774e-05</v>
+        <v>0.0001058280501714674</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0003770373845179628</v>
+        <v>5.881757280743408e-05</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0007701805118299186</v>
       </c>
     </row>
     <row r="5">
@@ -2072,19 +2351,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.1660671548213561</v>
+        <v>0.1845871007798583</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1602264086804516</v>
+        <v>0.1915092026633233</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1611061605034639</v>
+        <v>0.1810138589826415</v>
       </c>
       <c r="F5" t="n">
-        <v>0.153390510506188</v>
+        <v>0.1928323140197533</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1922007907997814</v>
+        <v>0.18251956874404</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.1762114424583076</v>
       </c>
     </row>
     <row r="6">
@@ -2099,19 +2381,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.007243479707863419</v>
+        <v>0.005042480402271255</v>
       </c>
       <c r="D6" t="n">
-        <v>0.004061232115372802</v>
+        <v>0.008085741894533292</v>
       </c>
       <c r="E6" t="n">
-        <v>0.01263017704095047</v>
+        <v>0.0105542128715875</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01041806254037231</v>
+        <v>0.003245928844365197</v>
       </c>
       <c r="G6" t="n">
-        <v>0.008409527874084237</v>
+        <v>0.007295583023951689</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0115449435138851</v>
       </c>
     </row>
     <row r="7">
@@ -2126,19 +2411,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.0230345935063257</v>
+        <v>0.01578620790147574</v>
       </c>
       <c r="D7" t="n">
-        <v>0.02016413890796424</v>
+        <v>0.01490702939350525</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03021652508231257</v>
+        <v>0.01681951611863231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0297820654617601</v>
+        <v>0.01510905149744946</v>
       </c>
       <c r="G7" t="n">
-        <v>0.01509142339822258</v>
+        <v>0.01628713638846735</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.01612374513632611</v>
       </c>
     </row>
     <row r="8">
@@ -2153,19 +2441,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1.184714068103687</v>
+        <v>1.10110132093701</v>
       </c>
       <c r="D8" t="n">
-        <v>1.160768489802872</v>
+        <v>1.041965181353495</v>
       </c>
       <c r="E8" t="n">
-        <v>1.400487474782525</v>
+        <v>1.333649338907844</v>
       </c>
       <c r="F8" t="n">
-        <v>1.159476164662244</v>
+        <v>0.9851888745392712</v>
       </c>
       <c r="G8" t="n">
-        <v>1.03703040917177</v>
+        <v>1.06428675217623</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.10219467791715</v>
       </c>
     </row>
     <row r="9">
@@ -2180,19 +2471,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2.453910397892429</v>
+        <v>2.439022734654755</v>
       </c>
       <c r="D9" t="n">
-        <v>2.588197392634018</v>
+        <v>2.353998129042985</v>
       </c>
       <c r="E9" t="n">
-        <v>2.485646782730244</v>
+        <v>2.387269605696456</v>
       </c>
       <c r="F9" t="n">
-        <v>2.387976534373423</v>
+        <v>2.402745119831542</v>
       </c>
       <c r="G9" t="n">
-        <v>2.35866664185634</v>
+        <v>2.424569009825378</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.632377661939389</v>
       </c>
     </row>
     <row r="10">
@@ -2207,19 +2501,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.3122232246746258</v>
+        <v>0.2775324913890554</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4143006059229598</v>
+        <v>0.4296375379658045</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1755159131870406</v>
+        <v>0.1848173221139383</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2849700497579374</v>
+        <v>0.3796352950050618</v>
       </c>
       <c r="G10" t="n">
-        <v>0.4279906101775363</v>
+        <v>0.1810768978981185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.2833657513251224</v>
       </c>
     </row>
     <row r="11">
@@ -2234,19 +2531,22 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6236199538234847</v>
+        <v>0.5851066331096996</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5775555927149743</v>
+        <v>0.7117171683448508</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5579543425437745</v>
+        <v>0.603893052654679</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6680205825307128</v>
+        <v>0.7074775972107268</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7095757429874614</v>
+        <v>0.4621589541732883</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5028466015295168</v>
       </c>
     </row>
   </sheetData>
